--- a/default_solv_candidate.xlsx
+++ b/default_solv_candidate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/sh19129_bristol_ac_uk/Documents/Documents/MyProject/ML/HSP_python/calculation/cal_20221227_solv_pred_v2/hsp_toolkit_solv_pred_v_2.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/xfang1_ic_ac_uk/Documents/Documents/My_code/SolvPred/hsp_toolkit_solv_pred_v_2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1194" documentId="11_F25DC773A252ABDACC1048E8991D7BDE5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E788B45-EB16-4A16-985D-9B20910B597B}"/>
+  <xr:revisionPtr revIDLastSave="1195" documentId="11_F25DC773A252ABDACC1048E8991D7BDE5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B8C827E-1DB3-472F-90AA-D6DA1E6EB621}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mix" sheetId="2" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>ethyl alcohol</t>
   </si>
   <si>
-    <t>Glycerol</t>
-  </si>
-  <si>
     <t>67-56-1</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>N-methylimidazole(NMI)</t>
+  </si>
+  <si>
+    <t>Diethylether</t>
   </si>
 </sst>
 </file>
@@ -473,10 +473,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77F644C-01AA-4210-8A08-C9E649D34503}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -489,10 +489,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,23 +500,23 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -553,10 +553,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -569,15 +569,15 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
         <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -593,26 +593,26 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -623,12 +623,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -843,15 +840,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{440AC86F-A7D9-4E52-9514-D7770551CDF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCC6C4B-3617-4EB2-A0A6-328E290B3C20}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -876,10 +877,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCC6C4B-3617-4EB2-A0A6-328E290B3C20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{440AC86F-A7D9-4E52-9514-D7770551CDF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>